--- a/TAM2.0_Sequencing_Prework_Integrated_v0.2.xlsx
+++ b/TAM2.0_Sequencing_Prework_Integrated_v0.2.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Notes — READ ME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="How to read" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Platform view — cross-geo" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="UK&amp;I" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Europe — other" sheetId="4" state="visible" r:id="rId4"/>
@@ -116,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -138,11 +138,55 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -189,6 +233,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -554,7 +600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A51"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="135" customWidth="1" min="1" max="1"/>
@@ -574,297 +620,132 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Notes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15" customHeight="1">
+          <t>How to read this workbook:</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>1. Unlike the PPT exercise we did for Genius, this is a geo × segment view.</t>
+          <t>• Each geo tab opens with the inputs: business priorities and corporate priorities, with the dates by which they must be met.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2. It takes business priorities and corporate priorities as inputs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+          <t>• The Milestones row (▼) places major proposition-related milestones over the horizon in which they land.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="28" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>3. It captures the current-state and target-state stack.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
+          <t>• Each workstream row shows the current-state stack, the target-state stack, and the planned actions across Now (H2 '26 – H1 '27), Next (H2 '27 – H1 '29) and Later (H2 '29+).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>4. It tracks BUILD, MIGRATE and DECOM decisions on a Now / Next / Later timeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>How to read each geo tab:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
+          <t>• Actions are tagged: [BUILD] target-state build · [MIGRATE] migration or thin-out · [STOP] stop-sell / stop-integration · [EXIT] decommission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>• Square brackets denote channel context where relevant, e.g. [Bank], [ISV], [Payrix].</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>• Content is scoped to TAM 2.0 — platform-rationalisation actions, not the full BAU roadmap. Where an action enables a stated business priority, the cell says so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>• The INPUTS box holds business priorities and corporate constraints, with the dates they must be met. Segment-level priorities (below) sit above the geo-level priorities captured on each tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="15" customHeight="1">
+          <t>• Data centre consolidation is tracked under the Global Infrastructure &amp; Security workstream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>• The Milestones row (▼) places proposition and corporate milestones over the horizon in which they land.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>• The table has one row per workstream: current-state stack, target-state stack, then Now / Next / Later actions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>• All timeline activities are TAM-scoped; BAU roadmap items are excluded. Where an activity directly enables a stated business priority, the cell says so: "[BUILD] … — enabling &lt;priority&gt;".</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
+          <t>• Blue text is a working hypothesis for validation. A blank cell is a request for input — not an indication that nothing is planned.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Aggregate priorities (segment-wide, 2026–27):</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>• Tags: [BUILD] = target-state build or adherence · [MIGRATE] = front-book switch, back-book migration or thin-out · [STOP] = stop-sell / stop-integration (frees capacity) · [EXIT] = decommission milestone.</t>
+          <t>• Standardization and platform unification (POM + TAM).</t>
         </is>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>• Channel / persona context is tagged inline in square brackets where relevant, e.g. [Bank], [ISV], [Wholesale].</t>
+          <t>• Onboarding and activation speed — the core growth bottleneck.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>• Data centre consolidation is tracked under the Global Infrastructure &amp; Security workstream.</t>
+          <t>• VAS monetization — lending, payments optimization, settlement.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>• Horizons: Now = H2 '26 – H1 '27 · Next = H2 '27 – H1 '29 · Later = H2 '29+.</t>
+          <t>• Execution discipline — customer commitments and large rollouts.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>• Blue text is a hypothesis to validate. A blank cell means we need your input — not that nothing is planned.</t>
-        </is>
-      </c>
-    </row>
+          <t>• Migration off legacy and reduction of fragmentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Terminology:</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
+          <t>Integrated segment priorities:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="56" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>• Sales motion = direct, partner-led, or self-serve.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
+          <t>• 2026 — Stabilize core growth engines (Payrix; close roadmap gaps across hGP and hWP). Accelerate merchant activation and partner growth in the US and UK. Payrix with in-person payments. Embedded Finance. Assist / Integrated. Monetize VAS (payouts, lending/EFE, fraud, tokenization) and increase multi-product attach rate. Solve ACH. CRM consolidation and fragmentation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>• Persona = the partner or customer type within a segment (e.g. Referral, Agent, ISO/Wholesale, Payfac, PFaaS).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>• Channel = digital, in-person, or omnichannel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>• Proposition = what the merchant buys (e.g. Genius S, WP360, Revenue Boost). Propositions are inputs and milestones, not an axis of this view.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>• Platform = the stack itself, current vs target.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>• Persona treatment: SMB is not split by persona; Integrated tags personas inline in brackets; Enterprise is to be decided.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>Open questions:</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>1. Which countries do we consider per region? We want to avoid the long tail.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>2. Enterprise: do we split by persona / vertical (region × top 1–4 verticals)? Decide before populating further.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>3. Reconcile platform retirement timelines with the data centre consolidation plan — preliminary view requested from infrastructure (an application kept for three years cannot sit in a data centre exiting in one).</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>4. North America is intentionally omitted from this June pack — it is sequenced for the Jul 20–21 in-person.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>5. All populated content is a straw man from the June QPRs and workshop discussions — validate or clear with the segment and geo leads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Aggregate priorities (segment-wide, 2026–27):</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>• Standardization and platform unification (POM + TAM).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>• Onboarding and activation speed — the core growth bottleneck.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>• VAS monetization — lending, payments optimization, settlement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>• Execution discipline — customer commitments and large rollouts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>• Migration off legacy and reduction of fragmentation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Integrated segment priorities:</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="56" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>• 2026 — Stabilize core growth engines (Payrix; close roadmap gaps across hGP and hWP). Accelerate merchant activation and partner growth in the US and UK. Payrix with in-person payments. Embedded Finance. Assist / Integrated. Monetize VAS (payouts, lending/EFE, fraud, tokenization) and increase multi-product attach rate. Solve ACH. CRM consolidation and fragmentation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
           <t>• 2027 — Converge onboarding, payments and reporting (reduce duplicate stacks). Embedded finance and VAS as primary growth drivers (lending, RTP, fraud, tokenization). Global partner expansion. Fully integrate the merchant lifecycle (onboard → activate → monetize).</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Integrated notes:</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>• Lens: platform / portfolio first, region second (per Ian Hillis) — hence the Platform view tab ahead of the geo tabs. Sub-domain tags in brackets: [Payrix] [PayFac] [EFE] [Assist] [IP] [Intl].</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>• Personas are tagged inline in square brackets rather than split into separate rows; confirm with segment leads whether any persona warrants its own breakout (diminishing returns expected).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>• Much of the platform content is North America-centred and will be sequenced in detail on Jul 20–21; it is captured on the Platform view tab so the cross-geo decisions (ACH, VAP, SF.com, Payrix) are visible to the June group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>• Populated as a straw man from the June 2026 Integrated &amp; Platforms QPR and workshop discussions — for reaction with the segment leads.</t>
         </is>
       </c>
     </row>
@@ -897,12 +778,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -920,11 +807,15 @@
 6. CRM consolidation (hGP) and Launchpad low-code self-enrolment</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -936,13 +827,23 @@
 • POSPortal → Jeffersonville move blocking Android device activation</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -2043,12 +1944,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -2063,11 +1970,15 @@
 3. Define the target path off the Integrapay dependency for UK Integrated</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -2077,13 +1988,23 @@
 • POS pilot challenges slowing UK expansion</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -3001,12 +2922,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -3019,11 +2946,15 @@
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -3031,13 +2962,23 @@
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -3919,12 +3860,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -3937,11 +3884,15 @@
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
@@ -3949,13 +3900,23 @@
           <t>(populate ahead of June workshop)</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
@@ -4837,12 +4798,18 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="16" t="n"/>
+      <c r="D3" s="16" t="n"/>
+      <c r="E3" s="16" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
@@ -4856,11 +4823,15 @@
 2. Confirm SMB vs Integrated ownership of the Oceania platform estate (eWay · Ezidebit · Integrapay)</t>
         </is>
       </c>
+      <c r="C4" s="16" t="n"/>
+      <c r="D4" s="16" t="n"/>
+      <c r="E4" s="16" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Corporate priorities / constraints</t>
+          <t>Corporate priorities</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -4869,13 +4840,23 @@
 • Global Gateway readiness in-region determines whether one-hop migration is feasible (avoid paying for two migrations)</t>
         </is>
       </c>
-    </row>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+    <row r="6"/>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
       <c r="A8" s="9" t="inlineStr">

--- a/TAM2.0_Sequencing_Prework_Integrated_v0.2.xlsx
+++ b/TAM2.0_Sequencing_Prework_Integrated_v0.2.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="How to read" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Platform view — cross-geo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="North America" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="UK&amp;I" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Europe — other" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="APAC" sheetId="5" state="visible" r:id="rId5"/>
@@ -55,6 +55,11 @@
       <sz val="13"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
@@ -80,11 +85,6 @@
     </font>
     <font>
       <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00595959"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -116,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -138,55 +138,11 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -203,38 +159,39 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -616,11 +573,10 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>June workshop pack: Europe · APAC · Oceania</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Workshop pack: Europe · APAC · Oceania (June) · North America (Jul 20–21)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -684,7 +640,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
@@ -727,7 +682,6 @@
         </is>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -774,51 +728,48 @@
     <row r="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>TAM 2.0 sequencing — Integrated · Platform view — cross-geo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
+          <t>TAM 2.0 sequencing — Integrated · North America</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Pre-seeded for the Jul 20–21 North America sequencing session.</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Business priorities</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>1. Stabilize Payrix — Cornerstone (platform integrity, reporting, reconciliation) and in-person payments; restore partner confidence and merchant activation
 2. Close roadmap gaps across the two IP books (hGP $1.3B / hWP $750M) to create growth and minimize attrition
 3. Embedded Finance — EFE–GP integration brings Capital to hGP Integrated ISVs; faster funding (RTP / P2A); iQ SMB widget distribution
 4. Monetize VAS via pilot motions — Fee Assist (surcharge), Disputes Defender, network payment tokens, account updater — particularly in PayFac
-5. Solve ACH pan-segment — the binding constraint on VAP retirement
+5. Solve ACH pan-segment — the binding constraint on VAP retirement (VAP serves North America only)
 6. CRM consolidation (hGP) and Launchpad low-code self-enrolment</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Corporate priorities</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>• ACH dependency — VAP cannot be retired while Payfacs and Payrix depend on its ACH; Express/CheckCommerce is US-only with disconnected reporting; hGP relies on third parties (DCS)
 • Aeropay PBB no longer commercially viable for Platforms — a pan-segment ACH solution with purpose-fit features is needed
@@ -827,86 +778,76 @@
 • POSPortal → Jeffersonville move blocking Android device activation</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="17" t="n"/>
-    </row>
-    <row r="6"/>
+    </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Current-state stack</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Target-state stack (validate)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Milestones ▼</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>▼ SF.com cutover Jul 13 '26 (surcharging + auto-boarding)
 ▼ Assist 2B date Jul 10 '26
 ▼ Payrix in-person payments GA (~2 PIs)</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>▼ PayFac optimization suite GA — managed AU Q3/Q4 '26, smart retries early '27
 ▼ VAP ACH decision unlocks VAP-to-Core migrations</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -931,7 +872,7 @@
           </r>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1008,32 +949,32 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] Payrix in-person payments experience [Payrix] — card-present acceptance and terminal management for ISVs (4 teams, ~2 PIs)
 • [BUILD] Assist card-present implementation [Assist] — embeddable React component on triPOS Cloud, letting ISVs embed full CP capability
 • [BUILD] Launch modern Android OS devices across merchant form factors [IP]</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] Align both IP books to the API 2.0 / Global API federated standard — converging hGP and hWP integration front doors
 • [MIGRATE] Begin converging duplicate integration stacks — enabling the 2027 priority to fully integrate the merchant lifecycle</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t>• [EXIT] Decommission duplicate integration front doors once partner migration completes</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1056,7 +997,7 @@
           </r>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1203,31 +1144,31 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t>• [MIGRATE] GPI SF.com → hCorp SF.com consolidation — cutover Jul 13 with surcharging and auto-boarding enablement [IP]
 • [BUILD] Launchpad seamless self-enrolment — low-code embed of the enrolment process, enabling the partner-led growth priority</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] Parallel onboarding and faster funding [EFE]
 • [BUILD] Converge boarding onto Ignition / the hWP party model as the target experience lands</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>• [EXIT] Decommission legacy partner boarding paths</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1248,7 +1189,7 @@
           </r>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1305,21 +1246,21 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] Progress hGP CRM consolidation in line with the pending CRM 2/3 decision</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1336,14 +1277,14 @@
               <color rgb="002F5496"/>
               <sz val="9"/>
             </rPr>
-            <t>• VAP (retirement gated on ACH)
+            <t>• VAP — NA only (retirement gated on ACH)
 • Express / CheckCommerce (US-only ACH)
 • Core
 • Third-party ACH (DCS) on hGP</t>
           </r>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1438,32 +1379,32 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>• [BUILD] Resolve the pan-segment ACH gap — decide between retaining VAP as an ACH-only platform behind Core/Express, or mirroring VAP with Fifth Third as ODFI behind Core (~$1.4M scope); this gates VAP retirement
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>• [BUILD] Resolve the pan-segment ACH gap — decide between retaining VAP as an ACH-only platform behind Core/Express, or mirroring VAP with Fifth Third as ODFI behind Core (~$1.4M scope); VAP serves NA only and this gates its retirement
 • [STOP] Aeropay Pay-by-Bank for Platforms — deprioritised (no longer commercially viable)</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>• [MIGRATE] VAP → Core migrations once the ACH path lands
 • [BUILD] Real-time payments / dynamic payouts for instant sub-merchant funding [PayFac]
 • [BUILD] Push to Account — single global payouts solution [PayFac]</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>• [EXIT] Retire VAP (gated on the ACH decision and migrations)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1486,7 +1427,7 @@
           </r>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1633,28 +1574,28 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] EFE–GP integration — Capital available to hGP Integrated ISVs, establishing the framework for future geo expansion [EFE]
 • [BUILD] Payrix VAS expansion — second lending provider (YouLend), Disputes Defender, network payment token, real-time payouts, account updater [Payrix]
 • [BUILD] Fee Assist (surcharge) for sub-merchants [PayFac]</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] PayFac full optimization suite to GA — managed account updater (Q3/Q4) with Pazien reporting; smart retries (early '27) [PayFac]
 • [BUILD] Distribute EFE through non-ISV channels (iQ SMB widget) — expanding the embedded-finance SAM</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr"/>
     </row>
     <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1676,7 +1617,7 @@
           </r>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1715,27 +1656,27 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] Payrix Cornerstone — reconciliation reporting, chargeback/payout stabilization and platform revenue integrity (4 teams, ~3 PIs) [Payrix]</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] Enhanced reporting intelligence layer — uniform data codification for reporting and reconciliation, aligned with Pazien direction
 • [BUILD] Automated merchant migration tooling — processor-to-processor moves for software platforms</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr"/>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Global Infrastructure &amp; Security (incl. data centres)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1810,22 +1751,22 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="15" t="inlineStr">
         <is>
           <t>• [MIGRATE] POSPortal → Jeffersonville distribution centre — resolve key-exchange issues blocking Android device activation</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1900,17 +1841,18 @@
           </r>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>• [MIGRATE] Converge onboarding, payments and reporting experiences — reducing duplicate stacks per the 2027 priority</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A3:F3"/>
@@ -1944,124 +1886,104 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Business priorities</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>1. Accelerate merchant activation and partner growth in the UK (2026 segment priority)
 2. UK expansion — currently behind plan given early pilot challenges [Intl]
 3. Define the target path off the Integrapay dependency for UK Integrated</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Corporate priorities</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>• UK Integrated currently leverages Integrapay — interim platform, not target state
 • Multi-SUN capability for direct debit required in market [Intl]
 • POS pilot challenges slowing UK expansion</t>
         </is>
       </c>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="17" t="n"/>
-    </row>
-    <row r="6"/>
+    </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Current-state stack</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Target-state stack (validate)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Milestones ▼</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>▼ UK POS pilot stabilisation</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr"/>
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2138,18 +2060,18 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
+      <c r="D10" s="15" t="inlineStr"/>
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr"/>
     </row>
     <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2296,22 +2218,22 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="D11" s="15" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] Align UK partner boarding to Ignition / the hWP party model as it lands</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr"/>
+      <c r="F11" s="15" t="inlineStr"/>
     </row>
     <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2368,17 +2290,17 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
+      <c r="D12" s="15" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2399,7 +2321,7 @@
           </r>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2494,26 +2416,26 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>• [MIGRATE] Define the target path off Integrapay for UK Integrated — sooner rather than later; align with the Global Gateway timeline to avoid a two-hop migration</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>• [BUILD] Multi-SUN direct debit capability — enabling the UK expansion priority [Intl]</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr"/>
+      <c r="F13" s="15" t="inlineStr"/>
     </row>
     <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2660,18 +2582,18 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
+      <c r="D14" s="15" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr"/>
     </row>
     <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2710,18 +2632,18 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr"/>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Global Infrastructure &amp; Security (incl. data centres)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2796,18 +2718,18 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2882,9 +2804,9 @@
           </r>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2922,116 +2844,96 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Business priorities</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>(populate ahead of June workshop)</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="17" t="n"/>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>(populate ahead of the workshop)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Corporate priorities</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>(populate ahead of June workshop)</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="17" t="n"/>
-    </row>
-    <row r="6"/>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>(populate ahead of the workshop)</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Current-state stack</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Target-state stack (validate)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Milestones ▼</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr"/>
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3108,18 +3010,18 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
+      <c r="D10" s="15" t="inlineStr"/>
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr"/>
     </row>
     <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3266,18 +3168,18 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
+      <c r="D11" s="15" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="15" t="inlineStr"/>
     </row>
     <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3334,18 +3236,18 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
+      <c r="D12" s="15" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr"/>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3440,18 +3342,18 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
+      <c r="D13" s="15" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr"/>
+      <c r="F13" s="15" t="inlineStr"/>
     </row>
     <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3598,18 +3500,18 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
+      <c r="D14" s="15" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr"/>
     </row>
     <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3648,18 +3550,18 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr"/>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Global Infrastructure &amp; Security (incl. data centres)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3734,18 +3636,18 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3820,9 +3722,9 @@
           </r>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3860,116 +3762,96 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Business priorities</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
-        <is>
-          <t>(populate ahead of June workshop)</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="17" t="n"/>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>(populate ahead of the workshop)</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Corporate priorities</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>(populate ahead of June workshop)</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="17" t="n"/>
-    </row>
-    <row r="6"/>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>(populate ahead of the workshop)</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Current-state stack</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Target-state stack (validate)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Milestones ▼</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr"/>
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4046,18 +3928,18 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
+      <c r="D10" s="15" t="inlineStr"/>
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr"/>
     </row>
     <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4204,18 +4086,18 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
+      <c r="D11" s="15" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="15" t="inlineStr"/>
     </row>
     <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4272,18 +4154,18 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
+      <c r="D12" s="15" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr"/>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr"/>
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4378,18 +4260,18 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr"/>
-      <c r="E13" s="14" t="inlineStr"/>
-      <c r="F13" s="14" t="inlineStr"/>
+      <c r="D13" s="15" t="inlineStr"/>
+      <c r="E13" s="15" t="inlineStr"/>
+      <c r="F13" s="15" t="inlineStr"/>
     </row>
     <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4536,18 +4418,18 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
+      <c r="D14" s="15" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr"/>
     </row>
     <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4586,18 +4468,18 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr"/>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Global Infrastructure &amp; Security (incl. data centres)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4672,18 +4554,18 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4758,9 +4640,9 @@
           </r>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -4798,122 +4680,102 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="16" customHeight="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>INPUTS</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4" ht="62" customHeight="1">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Business priorities</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>1. Consolidate Ezidebit promptly — onto Integrapay or TAM 2.0 target-state rails (Matt's ask)
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>1. Consolidate Ezidebit promptly — onto Integrapay or TAM 2.0 target-state rails
 2. Confirm SMB vs Integrated ownership of the Oceania platform estate (eWay · Ezidebit · Integrapay)</t>
         </is>
       </c>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="62" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Corporate priorities</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>• Ezidebit consolidation decision open — interim (Integrapay) vs direct-to-target path
-• Global Gateway readiness in-region determines whether one-hop migration is feasible (avoid paying for two migrations)</t>
-        </is>
-      </c>
-      <c r="C5" s="16" t="n"/>
-      <c r="D5" s="16" t="n"/>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="17" t="n"/>
-    </row>
-    <row r="6"/>
+• Global Gateway readiness in-region determines whether a one-hop migration is feasible (avoid paying for two migrations)</t>
+        </is>
+      </c>
+    </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>SEQUENCING</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Workstream</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Current-state stack</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Target-state stack (validate)</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Now (H2 '26 – H1 '27)</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Next (H2 '27 – H1 '29)</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>Later (H2 '29+)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>Milestones ▼</t>
         </is>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>▼ Ezidebit consolidation decision</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="12" t="inlineStr"/>
+      <c r="E9" s="13" t="inlineStr"/>
+      <c r="F9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="150" customHeight="1">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Single-in</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr"/>
+      <c r="C10" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4990,18 +4852,18 @@
           </r>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="14" t="inlineStr"/>
+      <c r="D10" s="15" t="inlineStr"/>
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr"/>
     </row>
     <row r="11" ht="150" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>Boarding</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr"/>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5148,18 +5010,18 @@
           </r>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr"/>
-      <c r="E11" s="14" t="inlineStr"/>
-      <c r="F11" s="14" t="inlineStr"/>
+      <c r="D11" s="15" t="inlineStr"/>
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="15" t="inlineStr"/>
     </row>
     <row r="12" ht="150" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Sales &amp; Servicing</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr"/>
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5216,17 +5078,17 @@
           </r>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr"/>
-      <c r="E12" s="14" t="inlineStr"/>
-      <c r="F12" s="14" t="inlineStr"/>
+      <c r="D12" s="15" t="inlineStr"/>
+      <c r="E12" s="15" t="inlineStr"/>
+      <c r="F12" s="15" t="inlineStr"/>
     </row>
     <row r="13" ht="150" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>Payment Processing</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5249,7 +5111,7 @@
           </r>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5344,31 +5206,31 @@
           </r>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t>• [MIGRATE] Consolidate Ezidebit — onto Integrapay or TAM 2.0 target-state rails (decision required; interim hop vs wait-for-target trade-off)
 • [STOP] Constrain new builds on eWay and Ezidebit to critical maintenance</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="15" t="inlineStr">
         <is>
           <t>• [MIGRATE] eWay — Debt Book tranche-2 candidate; migration path and timing to be confirmed against Global Gateway readiness</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="15" t="inlineStr">
         <is>
           <t>• [EXIT] Decommission consolidated legacy platforms</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>VAS</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5515,18 +5377,18 @@
           </r>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr"/>
-      <c r="E14" s="14" t="inlineStr"/>
-      <c r="F14" s="14" t="inlineStr"/>
+      <c r="D14" s="15" t="inlineStr"/>
+      <c r="E14" s="15" t="inlineStr"/>
+      <c r="F14" s="15" t="inlineStr"/>
     </row>
     <row r="15" ht="150" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>Unified Data and AI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr"/>
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5565,18 +5427,18 @@
           </r>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr"/>
-      <c r="E15" s="14" t="inlineStr"/>
-      <c r="F15" s="14" t="inlineStr"/>
+      <c r="D15" s="15" t="inlineStr"/>
+      <c r="E15" s="15" t="inlineStr"/>
+      <c r="F15" s="15" t="inlineStr"/>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="14" t="inlineStr">
         <is>
           <t>Global Infrastructure &amp; Security (incl. data centres)</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr"/>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5651,18 +5513,18 @@
           </r>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
+      <c r="D16" s="15" t="inlineStr"/>
+      <c r="E16" s="15" t="inlineStr"/>
+      <c r="F16" s="15" t="inlineStr"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>Single-out</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5737,9 +5599,9 @@
           </r>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr"/>
-      <c r="E17" s="14" t="inlineStr"/>
-      <c r="F17" s="14" t="inlineStr"/>
+      <c r="D17" s="15" t="inlineStr"/>
+      <c r="E17" s="15" t="inlineStr"/>
+      <c r="F17" s="15" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
